--- a/survey_templates/046_militarism_and_conflict_survey--survey_templates.xlsx
+++ b/survey_templates/046_militarism_and_conflict_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>How do you view militarism in general?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please describe your perception of militarism.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>militarism_attitudes</t>
+          <t>personal_experience</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>how_do_you_view_militarism</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Have you personally experienced conflict?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Yes, No, Don't know</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -561,23 +569,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>experience_conflict</t>
+          <t>conflict_resolution</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>have_you_personally_experienced</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What would you do to resolve a conflict?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please describe your approach to conflict resolution.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -589,15 +601,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>conflict_resolution</t>
+          <t>peace_efforts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>what_would_you_do</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What do you think is the most effective approach to peace efforts?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Describe your thoughts on peace efforts.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>peace_efforts</t>
+          <t>conflict_response</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>what_do_you_think</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>How do you respond to conflict?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Agree, Disagree, Neither</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -630,43 +650,51 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>conflict_resolution</t>
+          <t>importance_of_militarism</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>how_do_you_respond</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How important is it to address militarism?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Scale - 1-10</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please enter your email address</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Phone Number</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please enter your phone number</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,12 +736,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +759,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +782,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>conflict_resolution</t>
+          <t>contact_info_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>conflict_resolution</t>
+          <t>Contact Info 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +805,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>peace_efforts</t>
+          <t>conflict_resolution_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>peace_efforts</t>
+          <t>What do you think is the best way to resolve conflict?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +828,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>conflict_resolutions</t>
+          <t>militarism_attitudes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>conflict_resolutions</t>
+          <t>What is your attitude towards militarism?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +851,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>contact_info_2_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>Contact Info 2 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,23 +869,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>militarism_attitudes</t>
+          <t>conflict_resolution_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>militarism_attitudes</t>
+          <t>Conflict Resolution 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,12 +897,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>conflict_resolution_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>What do you do to resolve conflict?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +920,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>conflict_resolution</t>
+          <t>militarism_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>conflict_resolution</t>
+          <t>Militarism 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +943,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>conflict_resolution_2</t>
+          <t>peace_efforts_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>conflict_resolution_2</t>
+          <t>Peace Efforts 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>conflict_resolution_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>conflict_resolution_2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>conflict_resolution_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>conflict_resolution_2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>conflict_resolution_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>conflict_resolution_3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>militarism</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>militarism</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>militarism</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>militarism</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>militarism</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>militarism</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>militarism_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>militarism_2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +969,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,204 +997,153 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>militarism_attitudes_choices</t>
+          <t>personal_experience_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_highly',_'value':_'high'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'very_highly', 'value': 'high'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>militarism_attitudes_choices</t>
+          <t>personal_experience_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'not_at_all', 'value': 'not_at_all'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>militarism_attitudes_choices</t>
+          <t>personal_experience_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat',_'value':_'somewhat'}</t>
+          <t>don't_know</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat', 'value': 'somewhat'}</t>
+          <t>Don't know</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>militarism_attitudes_choices</t>
+          <t>conflict_response_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'not_at_all', 'value': 'not_at_all'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>experience_conflict_choices</t>
+          <t>conflict_response_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>experience_conflict_choices</t>
+          <t>conflict_response_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>Neither</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>peace_efforts_choices</t>
+          <t>conflict_resolution_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'very_important',_'value':_'very_important'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'very_important', 'value': 'very_important'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>peace_efforts_choices</t>
+          <t>conflict_resolution_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_important',_'value':_'somewhat_important'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat_important', 'value': 'somewhat_important'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>peace_efforts_choices</t>
+          <t>conflict_resolution_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'not_at_all', 'value': 'not_at_all'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>conflict_resolution_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'label':_'agree',_'value':_'agree'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'label': 'agree', 'value': 'agree'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>conflict_resolution_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'label':_'disagree',_'value':_'disagree'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'label': 'disagree', 'value': 'disagree'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>conflict_resolution_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'label':_'neither',_'value':_'neither'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'label': 'neither', 'value': 'neither'}</t>
+          <t>Neither</t>
         </is>
       </c>
     </row>
